--- a/data/trans_orig/IP07KS_C05_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C05_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21940</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13736</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34652</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11929</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7569</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16184</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36787</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>34497</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51633</t>
+          <t>49487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19718</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10140</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27408</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13592</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9219</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18167</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>43,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>34577</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42072</t>
+          <t>43752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,55%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>828</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34617</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25425</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44884</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12640</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8320</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18729</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44908</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48136</t>
+          <t>47771</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38373</t>
+          <t>37005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59635</t>
+          <t>58420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50313</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>40496</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>61736</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30175</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24142</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35912</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>57,08%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>25807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60920</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>80682</t>
+          <t>82792</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66675</t>
+          <t>70436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92435</t>
+          <t>94934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13586</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6745</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3349</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11647</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21179</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9429</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2762</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6635</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7428</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13693</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2843</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3284</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7469</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3312</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>13824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15447</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>52866</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>52866</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>52866</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>56435</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>56435</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>56435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>155644</t>
+          <t>158359</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>155644</t>
+          <t>158359</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>155644</t>
+          <t>158359</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39678</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31020</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>47574</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>61,2%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>24835</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8230</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42440</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40139</t>
+          <t>25842</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47799</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>64975</t>
+          <t>65520</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34041</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84392</t>
+          <t>76560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15373</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8896</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23162</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>42058</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21362</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>61464</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>58,27%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>56668</t>
+          <t>33242</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34425</t>
+          <t>23717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92202</t>
+          <t>43889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2576</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13672</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,14%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21,09%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3750</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8431</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>951</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>936</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9132</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4401</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2733</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9251</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>21631</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15179</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28854</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38,75%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>27,19%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>51,69%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>15263</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>10027</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>20602</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>38,52%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>37113</t>
+          <t>37396</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28690</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46151</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>24168</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17524</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>31267</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>31,39%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>56,01%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>24581</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>18288</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>30807</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>34,19%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>57,6%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>48870</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>60322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>9090</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>10859</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6844</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>16767</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>31,35%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>11820</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4152</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8463</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2781</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7704</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>868</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5733</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1632</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5154</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5295</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1632</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>5267</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>117866</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>101462</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>137781</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>37,56%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>51,01%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>64668</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>40955</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>79839</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>121557</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>103624</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>143032</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>186225</t>
+          <t>185184</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>155270</t>
+          <t>164115</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>214870</t>
+          <t>209276</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>109573</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>93460</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>125611</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>46,51%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>110406</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>91211</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>144134</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>52,65%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>43,49%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>108065</t>
+          <t>91760</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89311</t>
+          <t>79339</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>126741</t>
+          <t>103427</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>218472</t>
+          <t>201333</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>192521</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>261467</t>
+          <t>220995</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>22403</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>14945</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>33440</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>26242</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>17308</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>36855</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31940</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>48017</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>39370</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>9034</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>17382</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>7154</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>13524</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>11225</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>6064</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>19476</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>4400</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>11834</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>20713</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
